--- a/Temp_binned.xlsx
+++ b/Temp_binned.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Steffi Hodnett\MSc_Project\Project_Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Project\agg_model_MSc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54EBCCE-3ECE-42BA-9DD2-199C4F63AFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42708505-7CF1-4A97-86CB-F35F9938EC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4903659" sheetId="1" r:id="rId1"/>
@@ -21,393 +21,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="146">
   <si>
     <t>depth_bin</t>
-  </si>
-  <si>
-    <t>4903659_P1</t>
-  </si>
-  <si>
-    <t>4903659_P10</t>
-  </si>
-  <si>
-    <t>4903659_P11</t>
-  </si>
-  <si>
-    <t>4903659_P12</t>
-  </si>
-  <si>
-    <t>4903659_P14</t>
-  </si>
-  <si>
-    <t>4903659_P15</t>
-  </si>
-  <si>
-    <t>4903659_P16</t>
-  </si>
-  <si>
-    <t>4903659_P17</t>
-  </si>
-  <si>
-    <t>4903659_P18</t>
-  </si>
-  <si>
-    <t>4903659_P19</t>
-  </si>
-  <si>
-    <t>4903659_P2</t>
-  </si>
-  <si>
-    <t>4903659_P20</t>
-  </si>
-  <si>
-    <t>4903659_P21</t>
-  </si>
-  <si>
-    <t>4903659_P22</t>
-  </si>
-  <si>
-    <t>4903659_P23</t>
-  </si>
-  <si>
-    <t>4903659_P24</t>
-  </si>
-  <si>
-    <t>4903659_P25</t>
-  </si>
-  <si>
-    <t>4903659_P26</t>
-  </si>
-  <si>
-    <t>4903659_P27</t>
-  </si>
-  <si>
-    <t>4903659_P28</t>
-  </si>
-  <si>
-    <t>4903659_P29</t>
-  </si>
-  <si>
-    <t>4903659_P3</t>
-  </si>
-  <si>
-    <t>4903659_P30</t>
-  </si>
-  <si>
-    <t>4903659_P31</t>
-  </si>
-  <si>
-    <t>4903659_P32</t>
-  </si>
-  <si>
-    <t>4903659_P33</t>
-  </si>
-  <si>
-    <t>4903659_P34</t>
-  </si>
-  <si>
-    <t>4903659_P35</t>
-  </si>
-  <si>
-    <t>4903659_P36</t>
-  </si>
-  <si>
-    <t>4903659_P37</t>
-  </si>
-  <si>
-    <t>4903659_P38</t>
-  </si>
-  <si>
-    <t>4903659_P39</t>
-  </si>
-  <si>
-    <t>4903659_P4</t>
-  </si>
-  <si>
-    <t>4903659_P40</t>
-  </si>
-  <si>
-    <t>4903659_P41</t>
-  </si>
-  <si>
-    <t>4903659_P42</t>
-  </si>
-  <si>
-    <t>4903659_P43</t>
-  </si>
-  <si>
-    <t>4903659_P44</t>
-  </si>
-  <si>
-    <t>4903659_P5</t>
-  </si>
-  <si>
-    <t>4903659_P6</t>
-  </si>
-  <si>
-    <t>4903659_P7</t>
-  </si>
-  <si>
-    <t>4903659_P8</t>
-  </si>
-  <si>
-    <t>4903659_P9</t>
-  </si>
-  <si>
-    <t>6990636_P1</t>
-  </si>
-  <si>
-    <t>6990636_P10</t>
-  </si>
-  <si>
-    <t>6990636_P11</t>
-  </si>
-  <si>
-    <t>6990636_P12</t>
-  </si>
-  <si>
-    <t>6990636_P13</t>
-  </si>
-  <si>
-    <t>6990636_P14</t>
-  </si>
-  <si>
-    <t>6990636_P15</t>
-  </si>
-  <si>
-    <t>6990636_P16</t>
-  </si>
-  <si>
-    <t>6990636_P17</t>
-  </si>
-  <si>
-    <t>6990636_P18</t>
-  </si>
-  <si>
-    <t>6990636_P19</t>
-  </si>
-  <si>
-    <t>6990636_P2</t>
-  </si>
-  <si>
-    <t>6990636_P20</t>
-  </si>
-  <si>
-    <t>6990636_P21</t>
-  </si>
-  <si>
-    <t>6990636_P22</t>
-  </si>
-  <si>
-    <t>6990636_P23</t>
-  </si>
-  <si>
-    <t>6990636_P24</t>
-  </si>
-  <si>
-    <t>6990636_P25</t>
-  </si>
-  <si>
-    <t>6990636_P26</t>
-  </si>
-  <si>
-    <t>6990636_P27</t>
-  </si>
-  <si>
-    <t>6990636_P28</t>
-  </si>
-  <si>
-    <t>6990636_P29</t>
-  </si>
-  <si>
-    <t>6990636_P3</t>
-  </si>
-  <si>
-    <t>6990636_P30</t>
-  </si>
-  <si>
-    <t>6990636_P31</t>
-  </si>
-  <si>
-    <t>6990636_P32</t>
-  </si>
-  <si>
-    <t>6990636_P33</t>
-  </si>
-  <si>
-    <t>6990636_P34</t>
-  </si>
-  <si>
-    <t>6990636_P35</t>
-  </si>
-  <si>
-    <t>6990636_P36</t>
-  </si>
-  <si>
-    <t>6990636_P37</t>
-  </si>
-  <si>
-    <t>6990636_P38</t>
-  </si>
-  <si>
-    <t>6990636_P39</t>
-  </si>
-  <si>
-    <t>6990636_P4</t>
-  </si>
-  <si>
-    <t>6990636_P40</t>
-  </si>
-  <si>
-    <t>6990636_P41</t>
-  </si>
-  <si>
-    <t>6990636_P42</t>
-  </si>
-  <si>
-    <t>6990636_P43</t>
-  </si>
-  <si>
-    <t>6990636_P44</t>
-  </si>
-  <si>
-    <t>6990636_P45</t>
-  </si>
-  <si>
-    <t>6990636_P46</t>
-  </si>
-  <si>
-    <t>6990636_P47</t>
-  </si>
-  <si>
-    <t>6990636_P48</t>
-  </si>
-  <si>
-    <t>6990636_P49</t>
-  </si>
-  <si>
-    <t>6990636_P5</t>
-  </si>
-  <si>
-    <t>6990636_P50</t>
-  </si>
-  <si>
-    <t>6990636_P51</t>
-  </si>
-  <si>
-    <t>6990636_P52</t>
-  </si>
-  <si>
-    <t>6990636_P53</t>
-  </si>
-  <si>
-    <t>6990636_P54</t>
-  </si>
-  <si>
-    <t>6990636_P55</t>
-  </si>
-  <si>
-    <t>6990636_P56</t>
-  </si>
-  <si>
-    <t>6990636_P57</t>
-  </si>
-  <si>
-    <t>6990636_P58</t>
-  </si>
-  <si>
-    <t>6990636_P59</t>
-  </si>
-  <si>
-    <t>6990636_P6</t>
-  </si>
-  <si>
-    <t>6990636_P60</t>
-  </si>
-  <si>
-    <t>6990636_P61</t>
-  </si>
-  <si>
-    <t>6990636_P62</t>
-  </si>
-  <si>
-    <t>6990636_P63</t>
-  </si>
-  <si>
-    <t>6990636_P64</t>
-  </si>
-  <si>
-    <t>6990636_P65</t>
-  </si>
-  <si>
-    <t>6990636_P66</t>
-  </si>
-  <si>
-    <t>6990636_P67</t>
-  </si>
-  <si>
-    <t>6990636_P68</t>
-  </si>
-  <si>
-    <t>6990636_P69</t>
-  </si>
-  <si>
-    <t>6990636_P7</t>
-  </si>
-  <si>
-    <t>6990636_P70</t>
-  </si>
-  <si>
-    <t>6990636_P71</t>
-  </si>
-  <si>
-    <t>6990636_P73</t>
-  </si>
-  <si>
-    <t>6990636_P74</t>
-  </si>
-  <si>
-    <t>6990636_P75</t>
-  </si>
-  <si>
-    <t>6990636_P76</t>
-  </si>
-  <si>
-    <t>6990636_P77</t>
-  </si>
-  <si>
-    <t>6990636_P78</t>
-  </si>
-  <si>
-    <t>6990636_P79</t>
-  </si>
-  <si>
-    <t>6990636_P8</t>
-  </si>
-  <si>
-    <t>6990636_P80</t>
-  </si>
-  <si>
-    <t>6990636_P81</t>
-  </si>
-  <si>
-    <t>6990636_P82</t>
-  </si>
-  <si>
-    <t>6990636_P83</t>
-  </si>
-  <si>
-    <t>6990636_P84</t>
-  </si>
-  <si>
-    <t>6990636_P85</t>
-  </si>
-  <si>
-    <t>6990636_P86</t>
-  </si>
-  <si>
-    <t>6990636_P9</t>
   </si>
   <si>
     <t>0–10</t>
@@ -589,6 +205,261 @@
   <si>
     <t>1950–2000</t>
   </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P10</t>
+  </si>
+  <si>
+    <t>P11</t>
+  </si>
+  <si>
+    <t>P12</t>
+  </si>
+  <si>
+    <t>P14</t>
+  </si>
+  <si>
+    <t>P15</t>
+  </si>
+  <si>
+    <t>P16</t>
+  </si>
+  <si>
+    <t>P17</t>
+  </si>
+  <si>
+    <t>P18</t>
+  </si>
+  <si>
+    <t>P19</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P20</t>
+  </si>
+  <si>
+    <t>P21</t>
+  </si>
+  <si>
+    <t>P22</t>
+  </si>
+  <si>
+    <t>P23</t>
+  </si>
+  <si>
+    <t>P24</t>
+  </si>
+  <si>
+    <t>P25</t>
+  </si>
+  <si>
+    <t>P26</t>
+  </si>
+  <si>
+    <t>P27</t>
+  </si>
+  <si>
+    <t>P28</t>
+  </si>
+  <si>
+    <t>P29</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>P30</t>
+  </si>
+  <si>
+    <t>P31</t>
+  </si>
+  <si>
+    <t>P32</t>
+  </si>
+  <si>
+    <t>P33</t>
+  </si>
+  <si>
+    <t>P34</t>
+  </si>
+  <si>
+    <t>P35</t>
+  </si>
+  <si>
+    <t>P36</t>
+  </si>
+  <si>
+    <t>P37</t>
+  </si>
+  <si>
+    <t>P38</t>
+  </si>
+  <si>
+    <t>P39</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>P40</t>
+  </si>
+  <si>
+    <t>P41</t>
+  </si>
+  <si>
+    <t>P42</t>
+  </si>
+  <si>
+    <t>P43</t>
+  </si>
+  <si>
+    <t>P44</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>P6</t>
+  </si>
+  <si>
+    <t>P7</t>
+  </si>
+  <si>
+    <t>P8</t>
+  </si>
+  <si>
+    <t>P9</t>
+  </si>
+  <si>
+    <t>P13</t>
+  </si>
+  <si>
+    <t>P45</t>
+  </si>
+  <si>
+    <t>P46</t>
+  </si>
+  <si>
+    <t>P47</t>
+  </si>
+  <si>
+    <t>P48</t>
+  </si>
+  <si>
+    <t>P49</t>
+  </si>
+  <si>
+    <t>P50</t>
+  </si>
+  <si>
+    <t>P51</t>
+  </si>
+  <si>
+    <t>P52</t>
+  </si>
+  <si>
+    <t>P53</t>
+  </si>
+  <si>
+    <t>P54</t>
+  </si>
+  <si>
+    <t>P55</t>
+  </si>
+  <si>
+    <t>P56</t>
+  </si>
+  <si>
+    <t>P57</t>
+  </si>
+  <si>
+    <t>P58</t>
+  </si>
+  <si>
+    <t>P59</t>
+  </si>
+  <si>
+    <t>P60</t>
+  </si>
+  <si>
+    <t>P61</t>
+  </si>
+  <si>
+    <t>P62</t>
+  </si>
+  <si>
+    <t>P63</t>
+  </si>
+  <si>
+    <t>P64</t>
+  </si>
+  <si>
+    <t>P65</t>
+  </si>
+  <si>
+    <t>P66</t>
+  </si>
+  <si>
+    <t>P67</t>
+  </si>
+  <si>
+    <t>P68</t>
+  </si>
+  <si>
+    <t>P69</t>
+  </si>
+  <si>
+    <t>P70</t>
+  </si>
+  <si>
+    <t>P71</t>
+  </si>
+  <si>
+    <t>P73</t>
+  </si>
+  <si>
+    <t>P74</t>
+  </si>
+  <si>
+    <t>P75</t>
+  </si>
+  <si>
+    <t>P76</t>
+  </si>
+  <si>
+    <t>P77</t>
+  </si>
+  <si>
+    <t>P78</t>
+  </si>
+  <si>
+    <t>P79</t>
+  </si>
+  <si>
+    <t>P80</t>
+  </si>
+  <si>
+    <t>P81</t>
+  </si>
+  <si>
+    <t>P82</t>
+  </si>
+  <si>
+    <t>P83</t>
+  </si>
+  <si>
+    <t>P84</t>
+  </si>
+  <si>
+    <t>P85</t>
+  </si>
+  <si>
+    <t>P86</t>
+  </si>
 </sst>
 </file>
 
@@ -643,15 +514,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -954,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DX61"/>
+  <dimension ref="A1:DY61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -964,138 +831,138 @@
     <col min="44" max="44" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
@@ -1181,10 +1048,11 @@
       <c r="DV1" s="1"/>
       <c r="DW1" s="1"/>
       <c r="DX1" s="1"/>
+      <c r="DY1" s="1"/>
     </row>
-    <row r="2" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>9.4972491549295768</v>
@@ -1316,9 +1184,9 @@
         <v>11.20970043661972</v>
       </c>
     </row>
-    <row r="3" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>9.4968640000000004</v>
@@ -1447,9 +1315,9 @@
         <v>11.204814029411761</v>
       </c>
     </row>
-    <row r="4" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>131</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>9.4948879374999997</v>
@@ -1578,9 +1446,9 @@
         <v>11.1945408125</v>
       </c>
     </row>
-    <row r="5" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>132</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>9.4855462666666668</v>
@@ -1709,9 +1577,9 @@
         <v>11.02990914705882</v>
       </c>
     </row>
-    <row r="6" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>9.3415718333333349</v>
@@ -1840,9 +1708,9 @@
         <v>10.33865820588235</v>
       </c>
     </row>
-    <row r="7" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>134</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>9.2845289999999991</v>
@@ -1971,9 +1839,9 @@
         <v>10.14144172222222</v>
       </c>
     </row>
-    <row r="8" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>9.2132600333333343</v>
@@ -2102,9 +1970,9 @@
         <v>10.10067603125</v>
       </c>
     </row>
-    <row r="9" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>9.0527697647058822</v>
@@ -2233,9 +2101,9 @@
         <v>10.12842570588235</v>
       </c>
     </row>
-    <row r="10" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>137</v>
+        <v>9</v>
       </c>
       <c r="B10">
         <v>8.8916360937499999</v>
@@ -2364,9 +2232,9 @@
         <v>10.20373970588235</v>
       </c>
     </row>
-    <row r="11" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="B11">
         <v>8.807923588235294</v>
@@ -2495,9 +2363,9 @@
         <v>10.196558062499999</v>
       </c>
     </row>
-    <row r="12" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>139</v>
+        <v>11</v>
       </c>
       <c r="B12">
         <v>8.8176051451612896</v>
@@ -2626,9 +2494,9 @@
         <v>9.979682939393939</v>
       </c>
     </row>
-    <row r="13" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>8.8140032812500007</v>
@@ -2757,9 +2625,9 @@
         <v>9.6959123709677417</v>
       </c>
     </row>
-    <row r="14" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>141</v>
+        <v>13</v>
       </c>
       <c r="B14">
         <v>8.7788298225806454</v>
@@ -2888,9 +2756,9 @@
         <v>9.5131870781250001</v>
       </c>
     </row>
-    <row r="15" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>142</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>8.6390266774193538</v>
@@ -3019,9 +2887,9 @@
         <v>9.4684541718750008</v>
       </c>
     </row>
-    <row r="16" spans="1:128" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:129" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>143</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>8.5634175833333348</v>
@@ -3152,7 +3020,7 @@
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>144</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>8.4754052903225805</v>
@@ -3283,7 +3151,7 @@
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>145</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>8.4597081911764711</v>
@@ -3414,7 +3282,7 @@
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="B19">
         <v>8.4851416363636361</v>
@@ -3545,7 +3413,7 @@
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="B20">
         <v>8.35376115625</v>
@@ -3676,7 +3544,7 @@
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="B21">
         <v>8.3039322968750007</v>
@@ -3807,7 +3675,7 @@
     </row>
     <row r="22" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="B22">
         <v>8.2491089782608693</v>
@@ -3938,7 +3806,7 @@
     </row>
     <row r="23" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>150</v>
+        <v>22</v>
       </c>
       <c r="B23">
         <v>8.1347042199999997</v>
@@ -4069,7 +3937,7 @@
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="B24">
         <v>8.0464182708333336</v>
@@ -4200,7 +4068,7 @@
     </row>
     <row r="25" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="B25">
         <v>8.0732285208333341</v>
@@ -4331,7 +4199,7 @@
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="B26">
         <v>8.083068217391304</v>
@@ -4462,7 +4330,7 @@
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="B27">
         <v>7.9902908909090913</v>
@@ -4593,7 +4461,7 @@
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="B28">
         <v>7.9432137545454546</v>
@@ -4724,7 +4592,7 @@
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>7.8888800000000003</v>
@@ -4855,7 +4723,7 @@
     </row>
     <row r="30" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>157</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>7.7019137576923082</v>
@@ -4986,7 +4854,7 @@
     </row>
     <row r="31" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="B31">
         <v>7.5215650666666667</v>
@@ -5114,7 +4982,7 @@
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>159</v>
+        <v>31</v>
       </c>
       <c r="B32">
         <v>7.2384751140350874</v>
@@ -5245,7 +5113,7 @@
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="B33">
         <v>6.831442272131147</v>
@@ -5376,7 +5244,7 @@
     </row>
     <row r="34" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="B34">
         <v>6.5541482327868854</v>
@@ -5507,7 +5375,7 @@
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="B35">
         <v>6.0940480927272729</v>
@@ -5638,7 +5506,7 @@
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>163</v>
+        <v>35</v>
       </c>
       <c r="B36">
         <v>5.6928956158730157</v>
@@ -5769,7 +5637,7 @@
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>164</v>
+        <v>36</v>
       </c>
       <c r="B37">
         <v>5.3269881881355934</v>
@@ -5900,7 +5768,7 @@
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>165</v>
+        <v>37</v>
       </c>
       <c r="B38">
         <v>5.0292537080645161</v>
@@ -6031,7 +5899,7 @@
     </row>
     <row r="39" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>166</v>
+        <v>38</v>
       </c>
       <c r="B39">
         <v>4.8045680034482752</v>
@@ -6162,7 +6030,7 @@
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>167</v>
+        <v>39</v>
       </c>
       <c r="B40">
         <v>4.6247635186440679</v>
@@ -6293,7 +6161,7 @@
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>168</v>
+        <v>40</v>
       </c>
       <c r="B41">
         <v>4.4754963050847456</v>
@@ -6424,7 +6292,7 @@
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="B42">
         <v>4.3929024999999999</v>
@@ -6537,7 +6405,7 @@
     </row>
     <row r="43" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="L43">
         <v>4.2286784499999994</v>
@@ -6623,7 +6491,7 @@
     </row>
     <row r="44" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="L44">
         <v>4.1063948000000003</v>
@@ -6709,7 +6577,7 @@
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>172</v>
+        <v>44</v>
       </c>
       <c r="L45">
         <v>4.0344197333333334</v>
@@ -6795,7 +6663,7 @@
     </row>
     <row r="46" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="L46">
         <v>3.962371675</v>
@@ -6881,7 +6749,7 @@
     </row>
     <row r="47" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="L47">
         <v>3.8804071250000001</v>
@@ -6967,7 +6835,7 @@
     </row>
     <row r="48" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>175</v>
+        <v>47</v>
       </c>
       <c r="L48">
         <v>3.815885333333334</v>
@@ -7053,7 +6921,7 @@
     </row>
     <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>176</v>
+        <v>48</v>
       </c>
       <c r="L49">
         <v>3.7632243999999999</v>
@@ -7139,7 +7007,7 @@
     </row>
     <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>177</v>
+        <v>49</v>
       </c>
       <c r="L50">
         <v>3.7063598249999998</v>
@@ -7225,7 +7093,7 @@
     </row>
     <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="L51">
         <v>3.653501166666667</v>
@@ -7311,7 +7179,7 @@
     </row>
     <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>179</v>
+        <v>51</v>
       </c>
       <c r="L52">
         <v>3.6212494500000001</v>
@@ -7397,7 +7265,7 @@
     </row>
     <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>180</v>
+        <v>52</v>
       </c>
       <c r="L53">
         <v>3.6021106249999999</v>
@@ -7483,7 +7351,7 @@
     </row>
     <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="L54">
         <v>3.6099094749999998</v>
@@ -7569,7 +7437,7 @@
     </row>
     <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="L55">
         <v>3.6185984000000002</v>
@@ -7655,7 +7523,7 @@
     </row>
     <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="L56">
         <v>3.5840855999999999</v>
@@ -7741,7 +7609,7 @@
     </row>
     <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>184</v>
+        <v>56</v>
       </c>
       <c r="L57">
         <v>3.4732128000000002</v>
@@ -7827,7 +7695,7 @@
     </row>
     <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>185</v>
+        <v>57</v>
       </c>
       <c r="L58">
         <v>3.3467875999999999</v>
@@ -7910,7 +7778,7 @@
     </row>
     <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>186</v>
+        <v>58</v>
       </c>
       <c r="L59">
         <v>3.2649845750000002</v>
@@ -7990,7 +7858,7 @@
     </row>
     <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>187</v>
+        <v>59</v>
       </c>
       <c r="L60">
         <v>3.1587661749999998</v>
@@ -8067,7 +7935,7 @@
     </row>
     <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>188</v>
+        <v>60</v>
       </c>
       <c r="L61">
         <v>3.1106218999999999</v>
@@ -8146,7 +8014,7 @@
   <dimension ref="A1:CH61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8154,267 +8022,267 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>44</v>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="BG1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="BP1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="CH1" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="BP1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="BS1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="BT1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="BU1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="BV1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="BW1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BX1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="CA1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="CB1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>9.5044790499999987</v>
       </c>
       <c r="C2">
@@ -8672,9 +8540,9 @@
     </row>
     <row r="3" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3">
         <v>9.5031349285714288</v>
       </c>
       <c r="C3">
@@ -8932,9 +8800,9 @@
     </row>
     <row r="4" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4">
         <v>9.4991175999999999</v>
       </c>
       <c r="C4">
@@ -9192,9 +9060,9 @@
     </row>
     <row r="5" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5">
         <v>9.4943617777777778</v>
       </c>
       <c r="C5">
@@ -9452,9 +9320,9 @@
     </row>
     <row r="6" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6">
         <v>9.4326656875000001</v>
       </c>
       <c r="C6">
@@ -9712,9 +9580,9 @@
     </row>
     <row r="7" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7">
         <v>9.3211396666666655</v>
       </c>
       <c r="C7">
@@ -9972,9 +9840,9 @@
     </row>
     <row r="8" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8">
         <v>9.2527640625000007</v>
       </c>
       <c r="C8">
@@ -10232,9 +10100,9 @@
     </row>
     <row r="9" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9">
         <v>9.152259466666667</v>
       </c>
       <c r="C9">
@@ -10492,9 +10360,9 @@
     </row>
     <row r="10" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10">
         <v>8.910377200000001</v>
       </c>
       <c r="C10">
@@ -10752,9 +10620,9 @@
     </row>
     <row r="11" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11">
         <v>8.7682924666666668</v>
       </c>
       <c r="C11">
@@ -11012,9 +10880,9 @@
     </row>
     <row r="12" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12">
         <v>8.6729973666666655</v>
       </c>
       <c r="C12">
@@ -11272,9 +11140,9 @@
     </row>
     <row r="13" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13">
         <v>8.6573554516129025</v>
       </c>
       <c r="C13">
@@ -11532,9 +11400,9 @@
     </row>
     <row r="14" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14">
         <v>8.600428933333335</v>
       </c>
       <c r="C14">
@@ -11792,9 +11660,9 @@
     </row>
     <row r="15" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15">
         <v>8.5293600468750004</v>
       </c>
       <c r="C15">
@@ -12052,9 +11920,9 @@
     </row>
     <row r="16" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16">
         <v>8.4486235882352929</v>
       </c>
       <c r="C16">
@@ -12312,9 +12180,9 @@
     </row>
     <row r="17" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17">
         <v>8.4202610468749999</v>
       </c>
       <c r="C17">
@@ -12572,9 +12440,9 @@
     </row>
     <row r="18" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18">
         <v>8.396262419354839</v>
       </c>
       <c r="C18">
@@ -12832,9 +12700,9 @@
     </row>
     <row r="19" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19">
         <v>8.3885649999999998</v>
       </c>
       <c r="C19">
@@ -13092,9 +12960,9 @@
     </row>
     <row r="20" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20">
         <v>8.3019769687499991</v>
       </c>
       <c r="C20">
@@ -13352,9 +13220,9 @@
     </row>
     <row r="21" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21">
         <v>8.2444833787878782</v>
       </c>
       <c r="C21">
@@ -13612,9 +13480,9 @@
     </row>
     <row r="22" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22">
         <v>8.1937424199999995</v>
       </c>
       <c r="C22">
@@ -13872,9 +13740,9 @@
     </row>
     <row r="23" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23">
         <v>8.1610736875000001</v>
       </c>
       <c r="C23">
@@ -14132,9 +14000,9 @@
     </row>
     <row r="24" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24">
         <v>8.1048161200000006</v>
       </c>
       <c r="C24">
@@ -14392,9 +14260,9 @@
     </row>
     <row r="25" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25">
         <v>8.0101985083333336</v>
       </c>
       <c r="C25">
@@ -14652,9 +14520,9 @@
     </row>
     <row r="26" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26">
         <v>7.9912481166666671</v>
       </c>
       <c r="C26">
@@ -14912,9 +14780,9 @@
     </row>
     <row r="27" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27">
         <v>7.9430693130434777</v>
       </c>
       <c r="C27">
@@ -15172,9 +15040,9 @@
     </row>
     <row r="28" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28">
         <v>7.9485251363636369</v>
       </c>
       <c r="C28">
@@ -15432,9 +15300,9 @@
     </row>
     <row r="29" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29">
         <v>7.9385634454545464</v>
       </c>
       <c r="C29">
@@ -15692,9 +15560,9 @@
     </row>
     <row r="30" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30">
         <v>7.8036384478260867</v>
       </c>
       <c r="C30">
@@ -15952,9 +15820,9 @@
     </row>
     <row r="31" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31">
         <v>7.6469120923076934</v>
       </c>
       <c r="C31">
@@ -16212,9 +16080,9 @@
     </row>
     <row r="32" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32">
         <v>7.3300991366666661</v>
       </c>
       <c r="C32">
@@ -16472,9 +16340,9 @@
     </row>
     <row r="33" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33">
         <v>6.9195944836363639</v>
       </c>
       <c r="C33">
@@ -16732,9 +16600,9 @@
     </row>
     <row r="34" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34">
         <v>6.5335521253968256</v>
       </c>
       <c r="C34">
@@ -16992,9 +16860,9 @@
     </row>
     <row r="35" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35">
         <v>6.1316133220338989</v>
       </c>
       <c r="C35">
@@ -17252,9 +17120,9 @@
     </row>
     <row r="36" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36">
         <v>5.7268101285714286</v>
       </c>
       <c r="C36">
@@ -17512,9 +17380,9 @@
     </row>
     <row r="37" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37">
         <v>5.3603609790322579</v>
       </c>
       <c r="C37">
@@ -17772,9 +17640,9 @@
     </row>
     <row r="38" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38">
         <v>5.0767712810344827</v>
       </c>
       <c r="C38">
@@ -18032,9 +17900,9 @@
     </row>
     <row r="39" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39">
         <v>4.8234150344262297</v>
       </c>
       <c r="C39">
@@ -18292,9 +18160,9 @@
     </row>
     <row r="40" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40">
         <v>4.6522387593220333</v>
       </c>
       <c r="C40">
@@ -18552,9 +18420,9 @@
     </row>
     <row r="41" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41">
         <v>4.4917913526315791</v>
       </c>
       <c r="C41">
@@ -18812,9 +18680,9 @@
     </row>
     <row r="42" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42">
         <v>4.4024947166666673</v>
       </c>
       <c r="C42">
@@ -19072,7 +18940,7 @@
     </row>
     <row r="43" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="C43">
         <v>4.3166814250000014</v>
@@ -19329,7 +19197,7 @@
     </row>
     <row r="44" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="C44">
         <v>4.1926821749999998</v>
@@ -19586,7 +19454,7 @@
     </row>
     <row r="45" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>172</v>
+        <v>44</v>
       </c>
       <c r="C45">
         <v>4.1025901249999999</v>
@@ -19843,7 +19711,7 @@
     </row>
     <row r="46" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="C46">
         <v>4.0277795333333337</v>
@@ -20100,7 +19968,7 @@
     </row>
     <row r="47" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="C47">
         <v>3.9509327999999999</v>
@@ -20357,7 +20225,7 @@
     </row>
     <row r="48" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>175</v>
+        <v>47</v>
       </c>
       <c r="C48">
         <v>3.8741560499999999</v>
@@ -20614,7 +20482,7 @@
     </row>
     <row r="49" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>176</v>
+        <v>48</v>
       </c>
       <c r="C49">
         <v>3.8136206000000001</v>
@@ -20871,7 +20739,7 @@
     </row>
     <row r="50" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>177</v>
+        <v>49</v>
       </c>
       <c r="C50">
         <v>3.758188525</v>
@@ -21122,7 +20990,7 @@
     </row>
     <row r="51" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="C51">
         <v>3.7042487999999998</v>
@@ -21370,7 +21238,7 @@
     </row>
     <row r="52" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>179</v>
+        <v>51</v>
       </c>
       <c r="C52">
         <v>3.6623977999999999</v>
@@ -21618,7 +21486,7 @@
     </row>
     <row r="53" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>180</v>
+        <v>52</v>
       </c>
       <c r="C53">
         <v>3.635947133333334</v>
@@ -21866,7 +21734,7 @@
     </row>
     <row r="54" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="C54">
         <v>3.6090775750000001</v>
@@ -22114,7 +21982,7 @@
     </row>
     <row r="55" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="C55">
         <v>3.5845247499999999</v>
@@ -22362,7 +22230,7 @@
     </row>
     <row r="56" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="C56">
         <v>3.568902033333333</v>
@@ -22604,7 +22472,7 @@
     </row>
     <row r="57" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>184</v>
+        <v>56</v>
       </c>
       <c r="C57">
         <v>3.5585935499999999</v>
@@ -22846,7 +22714,7 @@
     </row>
     <row r="58" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>185</v>
+        <v>57</v>
       </c>
       <c r="C58">
         <v>3.5427417499999998</v>
@@ -23079,7 +22947,7 @@
     </row>
     <row r="59" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>186</v>
+        <v>58</v>
       </c>
       <c r="C59">
         <v>3.5246304749999999</v>
@@ -23306,7 +23174,7 @@
     </row>
     <row r="60" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>187</v>
+        <v>59</v>
       </c>
       <c r="C60">
         <v>3.500897133333333</v>
@@ -23518,7 +23386,7 @@
     </row>
     <row r="61" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>188</v>
+        <v>60</v>
       </c>
       <c r="C61">
         <v>3.4728420999999998</v>
